--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>85475739</v>
       </c>
       <c r="B2" t="n">
-        <v>107845</v>
+        <v>110013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622768.4883925782</v>
+        <v>622768</v>
       </c>
       <c r="R2" t="n">
-        <v>6929931.343996302</v>
+        <v>6929931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,19 +769,9 @@
           <t>2020-05-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>85475739</v>
       </c>
       <c r="B2" t="n">
-        <v>110013</v>
+        <v>110014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -757,11 +757,6 @@
       <c r="W2" t="inlineStr">
         <is>
           <t>Alnö</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Y-Sun-0384</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>85475739</v>
       </c>
       <c r="B2" t="n">
-        <v>110014</v>
+        <v>110017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>85475739</v>
       </c>
       <c r="B2" t="n">
-        <v>110120</v>
+        <v>110128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>85475739</v>
       </c>
       <c r="B2" t="n">
-        <v>110128</v>
+        <v>110130</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>85475739</v>
       </c>
       <c r="B2" t="n">
-        <v>110130</v>
+        <v>110138</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,6 +1534,132 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125086584</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98124</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Eriksdal, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>622237</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6929512</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>125086584</v>
       </c>
       <c r="B9" t="n">
-        <v>98124</v>
+        <v>98292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1539,12 +1539,7 @@
         <v>125086584</v>
       </c>
       <c r="B9" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1769,7 +1769,7 @@
         <v>132276443</v>
       </c>
       <c r="B11" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>132276430</v>
       </c>
       <c r="B10" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>132276443</v>
       </c>
       <c r="B11" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>132276430</v>
       </c>
       <c r="B10" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>132276443</v>
       </c>
       <c r="B11" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>132276430</v>
       </c>
       <c r="B10" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>132276443</v>
       </c>
       <c r="B11" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>132276430</v>
       </c>
       <c r="B10" t="n">
-        <v>57971</v>
+        <v>57978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>132276443</v>
       </c>
       <c r="B11" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>132276430</v>
       </c>
       <c r="B10" t="n">
-        <v>57978</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>132276443</v>
       </c>
       <c r="B11" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85475739</v>
+        <v>126459982</v>
       </c>
       <c r="B2" t="n">
-        <v>110138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222776</v>
+        <v>1662</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Bergviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Viola collina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Besser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -727,17 +722,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Koludden Hovid, Mpd</t>
+          <t>Metkroksvägen,vid stig längs standen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622768</v>
+        <v>622329</v>
       </c>
       <c r="R2" t="n">
-        <v>6929931</v>
+        <v>6929515</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,19 +754,29 @@
           <t>Alnö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Y-Sun-0363</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-16</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer fläckvis på många platser över hela udden.</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,16 +788,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gråalsumpskog på udde som tidigare varit barlastlokal</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -813,15 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86569744</v>
+        <v>123391651</v>
       </c>
       <c r="B3" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,50 +819,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eriksdal, vid stig genom albården, Eriksdal, Alnö, Mpd</t>
+          <t>Eriksdal, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622235.234537035</v>
+        <v>622344</v>
       </c>
       <c r="R3" t="n">
-        <v>6929534.030302397</v>
+        <v>6929756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,22 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,80 +909,74 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agneta Toomingas, Hans Johansson</t>
+          <t>Via Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101851513</v>
+        <v>98287455</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eriksdalsstigen, Mpd</t>
+          <t>Eriksdalsvägen, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622234.1728995312</v>
+        <v>622321</v>
       </c>
       <c r="R4" t="n">
-        <v>6929537.694318658</v>
+        <v>6929701</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1023,22 +1003,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,59 +1045,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101888358</v>
+        <v>123391643</v>
       </c>
       <c r="B5" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eriksdalsstigen, Mpd</t>
+          <t>Eriksdal, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622182.21162775</v>
+        <v>622344</v>
       </c>
       <c r="R5" t="n">
-        <v>6929639.931752862</v>
+        <v>6929756</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,22 +1126,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,80 +1156,72 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Via Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101887849</v>
+        <v>132276430</v>
       </c>
       <c r="B6" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Metkroksvägen, Sundsvall, Mpd</t>
+          <t>Eriksdal, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622304.896964943</v>
+        <v>622296</v>
       </c>
       <c r="R6" t="n">
-        <v>6929492.615752757</v>
+        <v>6929768</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,22 +1245,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,66 +1265,76 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Via Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104593851</v>
+        <v>123549383</v>
       </c>
       <c r="B7" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödprick</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia helvola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Eriksdalsvägen, Sundsvall, Mpd</t>
+          <t>Eriksdal, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622484.2202807327</v>
+        <v>622344</v>
       </c>
       <c r="R7" t="n">
-        <v>6929796.830346115</v>
+        <v>6929756</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1381,22 +1358,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,66 +1388,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Via Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104699477</v>
+        <v>99781490</v>
       </c>
       <c r="B8" t="n">
-        <v>73471</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>100077</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödprick</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia helvola</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsvall, Mpd</t>
+          <t>Eriksdal, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622553.3053717654</v>
+        <v>622144</v>
       </c>
       <c r="R8" t="n">
-        <v>6929783.63683442</v>
+        <v>6929575</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,22 +1473,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,22 +1503,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125086584</v>
+        <v>123391631</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>57945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,36 +1526,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>100110</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1585,13 +1562,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622237</v>
+        <v>622344</v>
       </c>
       <c r="R9" t="n">
-        <v>6929512</v>
+        <v>6929756</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,22 +1592,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,22 +1622,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Via Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132276430</v>
+        <v>123391653</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,21 +1645,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1690,7 +1667,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1704,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622296</v>
+        <v>622344</v>
       </c>
       <c r="R10" t="n">
-        <v>6929768</v>
+        <v>6929756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,12 +1711,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1873,6 +1860,1266 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123391632</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Eriksdal, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>622344</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6929756</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thomas Granfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Thomas Granfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>86569744</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Eriksdal, vid stig genom albården, Eriksdal, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>622235</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6929534</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-06-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-06-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas, Hans Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>101851513</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Eriksdalsstigen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>622235</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6929538</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125086584</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Eriksdal, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>622237</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6929512</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>102218082</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eriksdal stigen, Alnö, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>622247</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6929483</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>101888358</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eriksdalsstigen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>622182</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6929640</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100352512</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eriksdalsvägen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>622264</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6929689</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-04-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-04-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Hans Johansson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Hans Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>101887849</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Metkroksvägen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>622304</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6929493</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-06-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104593851</v>
+      </c>
+      <c r="B20" t="n">
+        <v>75261</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>96</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rödprick</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Arthonia helvola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eriksdalsvägen, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>622484</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6929797</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-10-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-10-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104699477</v>
+      </c>
+      <c r="B21" t="n">
+        <v>75261</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>96</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rödprick</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Arthonia helvola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>622553</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6929784</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-11-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>85475739</v>
+      </c>
+      <c r="B22" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Koludden Hovid, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>622768</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6929931</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Arkiv-Y-Sun-0170</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-05-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-05-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer fläckvis på många platser över hela udden.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gråalsumpskog på udde som tidigare varit barlastlokal</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51286-2024 artfynd.xlsx
+++ b/artfynd/A 51286-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104699477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126459982</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123391651</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98287455</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123391643</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132276430</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1613,6 +1653,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123549383</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99781490</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1847,6 +1897,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123391631</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1966,6 +2021,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123391653</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2075,6 +2135,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132276443</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2194,6 +2259,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123391632</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2308,6 +2378,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86569744</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2416,6 +2491,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101851513</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2537,6 +2617,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125086584</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2649,6 +2734,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102218082</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2752,6 +2842,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101888358</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2869,6 +2964,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100352512</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3007,6 +3107,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85475739</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3119,8 +3224,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101887849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>